--- a/document/TaskMan_ファイル一覧表.xlsx
+++ b/document/TaskMan_ファイル一覧表.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user113\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{693B0C28-EBC6-4B33-A021-103920142192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1EEB385-7A50-45B7-A315-68ED06CED1E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4A369B84-176A-4D0D-BFB9-664BDE7AD73A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="ファイル一覧" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="64">
   <si>
     <t>配置場所</t>
     <rPh sb="0" eb="4">
@@ -216,6 +216,241 @@
   </si>
   <si>
     <t>model.entityパッケージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>m_userテーブルにアクセスするDAOクラス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログイン情報を入力するフォーム画面</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログアウトしたことを表示する画面</t>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メニューを表示するメニュー画面</t>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスクの編集をするフォーム画面</t>
+    <rPh sb="4" eb="6">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスクの削除をするフォーム画面</t>
+    <rPh sb="4" eb="6">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスクの登録をするフォーム画面</t>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク登録に成功したことを表示する画面</t>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク一覧を表示する画面</t>
+    <rPh sb="3" eb="5">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク編集に成功したことを表示する画面</t>
+    <rPh sb="3" eb="5">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク削除に成功したことを表示する画面</t>
+    <rPh sb="3" eb="5">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク追加に失敗したことを表示する画面</t>
+    <rPh sb="3" eb="5">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シッパイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク編集に失敗したことを表示する画面</t>
+    <rPh sb="3" eb="5">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シッパイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク削除に失敗したことを表示する画面</t>
+    <rPh sb="3" eb="5">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シッパイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログイン処理を行うコントロールクラス</t>
+    <rPh sb="4" eb="6">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク一覧の表示を行うコントロールクラス</t>
+    <rPh sb="3" eb="5">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスクの情報変更処理を行うコントロールクラス</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク情報削除を行うコントロールクラス</t>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク登録処理を行うコントロールクラス</t>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カテゴリ情報を保持するentityクラス</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ホジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用者情報を保持するentityクラス</t>
+    <rPh sb="0" eb="5">
+      <t>リヨウシャジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ホジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステータス情報を保持するentityクラス</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ホジ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -262,9 +497,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -294,18 +532,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{35429287-11A2-4B0B-829A-C13AF3056B74}" name="テーブル2" displayName="テーブル2" ref="B2:G36" totalsRowShown="0">
-  <autoFilter ref="B2:G36" xr:uid="{35429287-11A2-4B0B-829A-C13AF3056B74}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{35429287-11A2-4B0B-829A-C13AF3056B74}" name="テーブル2" displayName="テーブル2" ref="B3:G36" totalsRowShown="0">
+  <autoFilter ref="B3:G36" xr:uid="{35429287-11A2-4B0B-829A-C13AF3056B74}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:G36">
+    <sortCondition ref="B3:B36"/>
+  </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{69642642-975E-4315-A040-B5AFDBF52485}" name="レイヤ" dataDxfId="1">
+    <tableColumn id="1" xr3:uid="{69642642-975E-4315-A040-B5AFDBF52485}" name="レイヤ" dataDxfId="2">
       <calculatedColumnFormula>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{01DED257-D073-4B65-A017-3191B199D407}" name="配置場所" dataDxfId="0">
+    <tableColumn id="2" xr3:uid="{01DED257-D073-4B65-A017-3191B199D407}" name="配置場所" dataDxfId="1">
       <calculatedColumnFormula>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{10D378EB-2420-4F6D-94EB-578C28C48887}" name="ファイル名"/>
     <tableColumn id="4" xr3:uid="{BD40918F-95FC-4779-9466-EEC593EC9C60}" name="内容"/>
-    <tableColumn id="5" xr3:uid="{61E9B625-6B0A-43DC-B4E2-261AFA95DB79}" name="ファイル種類" dataDxfId="2">
+    <tableColumn id="5" xr3:uid="{61E9B625-6B0A-43DC-B4E2-261AFA95DB79}" name="ファイル種類" dataDxfId="0">
       <calculatedColumnFormula>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{339BCFBD-8ACC-4A6E-AE26-4A3C9DF9F927}" name="ファイル種類番号"/>
@@ -631,7 +872,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1C5B600-9E48-4077-B262-F985B8C16AE8}">
-  <dimension ref="B2:G36"/>
+  <dimension ref="B3:G36"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="5" width="25.625" customWidth="1"/>
@@ -639,90 +880,73 @@
     <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B2" t="s">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>0</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E3" t="s">
         <v>2</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F3" t="s">
         <v>32</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>Model</v>
-      </c>
-      <c r="C3" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>model.daoパッケージ</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>ConnectionManager</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>Model</v>
+        <v>Controller</v>
       </c>
       <c r="C4" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>model.daoパッケージ</v>
+        <v>servletパッケージ</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="F4" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>DAO</v>
+        <v>Seavlet</v>
       </c>
       <c r="G4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>Model</v>
+        <v>Controller</v>
       </c>
       <c r="C5" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>model.entityパッケージ</v>
+        <v>servletパッケージ</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="F5" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>Bean</v>
+        <v>Seavlet</v>
       </c>
       <c r="G5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>Controller</v>
@@ -732,7 +956,10 @@
         <v>servletパッケージ</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="F6" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
@@ -742,157 +969,181 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
+        <v>Controller</v>
+      </c>
+      <c r="C7" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
+        <v>servletパッケージ</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>Seavlet</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B8" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
+        <v>Controller</v>
+      </c>
+      <c r="C8" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
+        <v>servletパッケージ</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>Seavlet</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B9" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
+        <v>Model</v>
+      </c>
+      <c r="C9" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
+        <v>model.daoパッケージ</v>
+      </c>
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>DAO</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B10" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
+        <v>Model</v>
+      </c>
+      <c r="C10" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
+        <v>model.entityパッケージ</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>Bean</v>
+      </c>
+      <c r="G10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
+        <v>Model</v>
+      </c>
+      <c r="C11" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
+        <v>model.entityパッケージ</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>Bean</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B12" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
+        <v>Model</v>
+      </c>
+      <c r="C12" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
+        <v>model.entityパッケージ</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>Bean</v>
+      </c>
+      <c r="G12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B13" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
+        <v>Model</v>
+      </c>
+      <c r="C13" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
+        <v>model.daoパッケージ</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>ConnectionManager</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B14" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>View</v>
       </c>
-      <c r="C7" t="str">
+      <c r="C14" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
         <v>webapp</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D14" t="s">
         <v>5</v>
       </c>
-      <c r="F7" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>jspファイル</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>View</v>
-      </c>
-      <c r="C8" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>webapp</v>
-      </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>jspファイル</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>View</v>
-      </c>
-      <c r="C9" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>webapp</v>
-      </c>
-      <c r="D9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>jspファイル</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>View</v>
-      </c>
-      <c r="C10" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>webapp</v>
-      </c>
-      <c r="D10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>jspファイル</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>View</v>
-      </c>
-      <c r="C11" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>webapp</v>
-      </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>jspファイル</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>View</v>
-      </c>
-      <c r="C12" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>webapp</v>
-      </c>
-      <c r="D12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>jspファイル</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>View</v>
-      </c>
-      <c r="C13" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>webapp</v>
-      </c>
-      <c r="D13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>jspファイル</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>View</v>
-      </c>
-      <c r="C14" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>webapp</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
+      <c r="E14" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="F14" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
@@ -902,7 +1153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>View</v>
@@ -912,7 +1163,10 @@
         <v>webapp</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>6</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="F15" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
@@ -922,7 +1176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>View</v>
@@ -932,7 +1186,10 @@
         <v>webapp</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="F16" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
@@ -942,127 +1199,145 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>Controller</v>
+        <v>View</v>
       </c>
       <c r="C17" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>servletパッケージ</v>
+        <v>webapp</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>8</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="F17" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>Seavlet</v>
+        <v>jspファイル</v>
       </c>
       <c r="G17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>Controller</v>
+        <v>View</v>
       </c>
       <c r="C18" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>servletパッケージ</v>
+        <v>webapp</v>
       </c>
       <c r="D18" t="s">
-        <v>20</v>
+        <v>9</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="F18" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>Seavlet</v>
+        <v>jspファイル</v>
       </c>
       <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>Controller</v>
+        <v>View</v>
       </c>
       <c r="C19" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>servletパッケージ</v>
+        <v>webapp</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>10</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="F19" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>Seavlet</v>
+        <v>jspファイル</v>
       </c>
       <c r="G19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>Controller</v>
+        <v>View</v>
       </c>
       <c r="C20" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>servletパッケージ</v>
+        <v>webapp</v>
       </c>
       <c r="D20" t="s">
-        <v>22</v>
+        <v>11</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="F20" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>Seavlet</v>
+        <v>jspファイル</v>
       </c>
       <c r="G20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>Model</v>
+        <v>View</v>
       </c>
       <c r="C21" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>model.entityパッケージ</v>
+        <v>webapp</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>12</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="F21" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>Bean</v>
+        <v>jspファイル</v>
       </c>
       <c r="G21">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>Model</v>
+        <v>View</v>
       </c>
       <c r="C22" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>model.entityパッケージ</v>
+        <v>webapp</v>
       </c>
       <c r="D22" t="s">
-        <v>24</v>
+        <v>13</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="F22" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>Bean</v>
+        <v>jspファイル</v>
       </c>
       <c r="G22">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>View</v>
@@ -1072,7 +1347,10 @@
         <v>webapp</v>
       </c>
       <c r="D23" t="s">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="F23" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
@@ -1082,7 +1360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>View</v>
@@ -1094,6 +1372,9 @@
       <c r="D24" t="s">
         <v>29</v>
       </c>
+      <c r="E24" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="F24" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>jspファイル</v>
@@ -1102,7 +1383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>View</v>
@@ -1114,6 +1395,9 @@
       <c r="D25" t="s">
         <v>30</v>
       </c>
+      <c r="E25" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="F25" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>jspファイル</v>
@@ -1122,7 +1406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>View</v>
@@ -1134,6 +1418,9 @@
       <c r="D26" t="s">
         <v>31</v>
       </c>
+      <c r="E26" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="F26" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>jspファイル</v>
@@ -1142,7 +1429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>#N/A</v>
@@ -1151,12 +1438,13 @@
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
         <v>#N/A</v>
       </c>
+      <c r="E27" s="1"/>
       <c r="F27" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>#N/A</v>
@@ -1165,12 +1453,13 @@
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
         <v>#N/A</v>
       </c>
+      <c r="E28" s="1"/>
       <c r="F28" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>#N/A</v>
@@ -1179,12 +1468,13 @@
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
         <v>#N/A</v>
       </c>
+      <c r="E29" s="1"/>
       <c r="F29" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>#N/A</v>
@@ -1193,12 +1483,13 @@
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
         <v>#N/A</v>
       </c>
+      <c r="E30" s="1"/>
       <c r="F30" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="31" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>#N/A</v>
@@ -1207,12 +1498,13 @@
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
         <v>#N/A</v>
       </c>
+      <c r="E31" s="1"/>
       <c r="F31" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="32" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>#N/A</v>
@@ -1221,12 +1513,13 @@
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
         <v>#N/A</v>
       </c>
+      <c r="E32" s="1"/>
       <c r="F32" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>#N/A</v>
@@ -1235,12 +1528,13 @@
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
         <v>#N/A</v>
       </c>
+      <c r="E33" s="1"/>
       <c r="F33" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>#N/A</v>
@@ -1249,12 +1543,13 @@
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
         <v>#N/A</v>
       </c>
+      <c r="E34" s="1"/>
       <c r="F34" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="35" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B35" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>#N/A</v>
@@ -1263,12 +1558,13 @@
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
         <v>#N/A</v>
       </c>
+      <c r="E35" s="1"/>
       <c r="F35" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="36" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>#N/A</v>
@@ -1277,6 +1573,7 @@
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
         <v>#N/A</v>
       </c>
+      <c r="E36" s="1"/>
       <c r="F36" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>#N/A</v>
@@ -1371,6 +1668,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/document/TaskMan_ファイル一覧表.xlsx
+++ b/document/TaskMan_ファイル一覧表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user113\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1EEB385-7A50-45B7-A315-68ED06CED1E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A5A67B-AB1A-42E9-B2BA-1DB1DC467E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4A369B84-176A-4D0D-BFB9-664BDE7AD73A}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="65">
   <si>
     <t>配置場所</t>
     <rPh sb="0" eb="4">
@@ -451,6 +451,10 @@
     <rPh sb="8" eb="10">
       <t>ホジ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>task-add-form-confirm.jsp</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1430,48 +1434,67 @@
       </c>
     </row>
     <row r="27" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C27" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E27" s="1"/>
-      <c r="F27" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>#N/A</v>
+      <c r="B27" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
+        <v>View</v>
+      </c>
+      <c r="C27" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
+        <v>webapp</v>
+      </c>
+      <c r="D27" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>jspファイル</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C28" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E28" s="1"/>
-      <c r="F28" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>#N/A</v>
+      <c r="B28" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
+        <v>View</v>
+      </c>
+      <c r="C28" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
+        <v>webapp</v>
+      </c>
+      <c r="D28" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>jspファイル</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C29" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>#N/A</v>
+      <c r="B29" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
+        <v>View</v>
+      </c>
+      <c r="C29" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
+        <v>webapp</v>
       </c>
       <c r="E29" s="1"/>
-      <c r="F29" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>#N/A</v>
+      <c r="F29" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>jspファイル</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">

--- a/document/TaskMan_ファイル一覧表.xlsx
+++ b/document/TaskMan_ファイル一覧表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A5A67B-AB1A-42E9-B2BA-1DB1DC467E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7D975A-3A0C-4684-8F8B-B76FB42F0E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4A369B84-176A-4D0D-BFB9-664BDE7AD73A}"/>
   </bookViews>

--- a/document/TaskMan_ファイル一覧表.xlsx
+++ b/document/TaskMan_ファイル一覧表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user113\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7D975A-3A0C-4684-8F8B-B76FB42F0E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2BE858-781A-4C30-975F-237FDD821F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4A369B84-176A-4D0D-BFB9-664BDE7AD73A}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="74">
   <si>
     <t>配置場所</t>
     <rPh sb="0" eb="4">
@@ -329,16 +329,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>タスク追加に失敗したことを表示する画面</t>
-    <rPh sb="3" eb="5">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>シッパイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>タスク編集に失敗したことを表示する画面</t>
     <rPh sb="3" eb="5">
       <t>ヘンシュウ</t>
@@ -454,7 +444,80 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>task-add-form-confirm.jsp</t>
+    <t>対応ユースケース</t>
+    <rPh sb="0" eb="2">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク一覧表示</t>
+    <rPh sb="3" eb="5">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログイン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク編集</t>
+    <rPh sb="3" eb="5">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク削除</t>
+    <rPh sb="3" eb="5">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク登録</t>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログイン/ログアウト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク登録/タスク編集</t>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システム全般</t>
+    <rPh sb="4" eb="6">
+      <t>ゼンパン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログアウト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク登録に失敗したことを表示する画面</t>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シッパイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -512,7 +575,10 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -536,21 +602,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{35429287-11A2-4B0B-829A-C13AF3056B74}" name="テーブル2" displayName="テーブル2" ref="B3:G36" totalsRowShown="0">
-  <autoFilter ref="B3:G36" xr:uid="{35429287-11A2-4B0B-829A-C13AF3056B74}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:G36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{35429287-11A2-4B0B-829A-C13AF3056B74}" name="テーブル2" displayName="テーブル2" ref="B3:H36" totalsRowShown="0">
+  <autoFilter ref="B3:H36" xr:uid="{35429287-11A2-4B0B-829A-C13AF3056B74}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:H36">
     <sortCondition ref="B3:B36"/>
   </sortState>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{69642642-975E-4315-A040-B5AFDBF52485}" name="レイヤ" dataDxfId="2">
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{69642642-975E-4315-A040-B5AFDBF52485}" name="レイヤ" dataDxfId="3">
       <calculatedColumnFormula>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{01DED257-D073-4B65-A017-3191B199D407}" name="配置場所" dataDxfId="1">
+    <tableColumn id="2" xr3:uid="{01DED257-D073-4B65-A017-3191B199D407}" name="配置場所" dataDxfId="2">
       <calculatedColumnFormula>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{10D378EB-2420-4F6D-94EB-578C28C48887}" name="ファイル名"/>
     <tableColumn id="4" xr3:uid="{BD40918F-95FC-4779-9466-EEC593EC9C60}" name="内容"/>
-    <tableColumn id="5" xr3:uid="{61E9B625-6B0A-43DC-B4E2-261AFA95DB79}" name="ファイル種類" dataDxfId="0">
+    <tableColumn id="8" xr3:uid="{17803444-57CA-4498-913B-24461371C283}" name="対応ユースケース" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{61E9B625-6B0A-43DC-B4E2-261AFA95DB79}" name="ファイル種類" dataDxfId="1">
       <calculatedColumnFormula>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{339BCFBD-8ACC-4A6E-AE26-4A3C9DF9F927}" name="ファイル種類番号"/>
@@ -876,15 +943,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1C5B600-9E48-4077-B262-F985B8C16AE8}">
-  <dimension ref="B3:G36"/>
+  <dimension ref="B3:H36"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="5" width="25.625" customWidth="1"/>
-    <col min="6" max="6" width="19.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="25.625" customWidth="1"/>
+    <col min="7" max="7" width="19.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
         <v>4</v>
       </c>
@@ -898,13 +965,16 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G3" t="s">
         <v>32</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>Controller</v>
@@ -917,17 +987,20 @@
         <v>16</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" t="str">
+        <v>55</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>Seavlet</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>Controller</v>
@@ -940,17 +1013,20 @@
         <v>15</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F5" t="str">
+        <v>56</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>Seavlet</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>Controller</v>
@@ -963,17 +1039,20 @@
         <v>20</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F6" t="str">
+        <v>57</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>Seavlet</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>Controller</v>
@@ -986,17 +1065,20 @@
         <v>21</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" t="str">
+        <v>58</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>Seavlet</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>Controller</v>
@@ -1009,17 +1091,20 @@
         <v>22</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" t="str">
+        <v>59</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>Seavlet</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>Model</v>
@@ -1034,15 +1119,18 @@
       <c r="E9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F9" t="str">
+      <c r="F9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>DAO</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>Model</v>
@@ -1055,17 +1143,20 @@
         <v>17</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F10" t="str">
+        <v>61</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>Bean</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>Model</v>
@@ -1078,17 +1169,20 @@
         <v>23</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" t="str">
+        <v>60</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>Bean</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>Model</v>
@@ -1101,17 +1195,20 @@
         <v>24</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F12" t="str">
+        <v>62</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>Bean</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>Model</v>
@@ -1126,15 +1223,18 @@
       <c r="E13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F13" t="str">
+      <c r="F13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>ConnectionManager</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>View</v>
@@ -1149,15 +1249,18 @@
       <c r="E14" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F14" t="str">
+      <c r="F14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>jspファイル</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>View</v>
@@ -1172,15 +1275,18 @@
       <c r="E15" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F15" t="str">
+      <c r="F15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>jspファイル</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>View</v>
@@ -1195,15 +1301,18 @@
       <c r="E16" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F16" t="str">
+      <c r="F16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>jspファイル</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>View</v>
@@ -1218,15 +1327,18 @@
       <c r="E17" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F17" t="str">
+      <c r="F17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>jspファイル</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>View</v>
@@ -1241,15 +1353,18 @@
       <c r="E18" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F18" t="str">
+      <c r="F18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G18" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>jspファイル</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>View</v>
@@ -1264,15 +1379,18 @@
       <c r="E19" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F19" t="str">
+      <c r="F19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>jspファイル</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>View</v>
@@ -1287,15 +1405,18 @@
       <c r="E20" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F20" t="str">
+      <c r="F20" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>jspファイル</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>View</v>
@@ -1310,15 +1431,18 @@
       <c r="E21" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F21" t="str">
+      <c r="F21" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G21" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>jspファイル</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>View</v>
@@ -1333,15 +1457,18 @@
       <c r="E22" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F22" t="str">
+      <c r="F22" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G22" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>jspファイル</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>View</v>
@@ -1356,15 +1483,18 @@
       <c r="E23" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F23" t="str">
+      <c r="F23" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G23" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>jspファイル</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>View</v>
@@ -1377,17 +1507,20 @@
         <v>29</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F24" t="str">
+        <v>73</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>jspファイル</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>View</v>
@@ -1400,17 +1533,20 @@
         <v>30</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F25" t="str">
+        <v>53</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G25" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>jspファイル</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>View</v>
@@ -1423,81 +1559,68 @@
         <v>31</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F26" t="str">
+        <v>54</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G26" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>jspファイル</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>View</v>
-      </c>
-      <c r="C27" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>webapp</v>
-      </c>
-      <c r="D27" t="s">
-        <v>64</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F27" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>jspファイル</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>View</v>
-      </c>
-      <c r="C28" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>webapp</v>
-      </c>
-      <c r="D28" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F28" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>jspファイル</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>View</v>
-      </c>
-      <c r="C29" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>webapp</v>
+    <row r="27" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B27" t="e">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C27" t="e">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" t="e">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B28" t="e">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C28" t="e">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" t="e">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" t="e">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C29" t="e">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
+        <v>#N/A</v>
       </c>
       <c r="E29" s="1"/>
-      <c r="F29" t="str">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>jspファイル</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F29" s="1"/>
+      <c r="G29" t="e">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>#N/A</v>
@@ -1507,12 +1630,13 @@
         <v>#N/A</v>
       </c>
       <c r="E30" s="1"/>
-      <c r="F30" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F30" s="1"/>
+      <c r="G30" t="e">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>#N/A</v>
@@ -1522,12 +1646,13 @@
         <v>#N/A</v>
       </c>
       <c r="E31" s="1"/>
-      <c r="F31" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F31" s="1"/>
+      <c r="G31" t="e">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>#N/A</v>
@@ -1537,12 +1662,13 @@
         <v>#N/A</v>
       </c>
       <c r="E32" s="1"/>
-      <c r="F32" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F32" s="1"/>
+      <c r="G32" t="e">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>#N/A</v>
@@ -1552,12 +1678,13 @@
         <v>#N/A</v>
       </c>
       <c r="E33" s="1"/>
-      <c r="F33" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F33" s="1"/>
+      <c r="G33" t="e">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>#N/A</v>
@@ -1567,12 +1694,13 @@
         <v>#N/A</v>
       </c>
       <c r="E34" s="1"/>
-      <c r="F34" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F34" s="1"/>
+      <c r="G34" t="e">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B35" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>#N/A</v>
@@ -1582,12 +1710,13 @@
         <v>#N/A</v>
       </c>
       <c r="E35" s="1"/>
-      <c r="F35" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F35" s="1"/>
+      <c r="G35" t="e">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
         <v>#N/A</v>
@@ -1597,7 +1726,8 @@
         <v>#N/A</v>
       </c>
       <c r="E36" s="1"/>
-      <c r="F36" t="e">
+      <c r="F36" s="1"/>
+      <c r="G36" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>#N/A</v>
       </c>

--- a/document/TaskMan_ファイル一覧表.xlsx
+++ b/document/TaskMan_ファイル一覧表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user113\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2BE858-781A-4C30-975F-237FDD821F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E207C061-67E4-433F-9804-E77AFFF98CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4A369B84-176A-4D0D-BFB9-664BDE7AD73A}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="78">
   <si>
     <t>配置場所</t>
     <rPh sb="0" eb="4">
@@ -517,6 +517,28 @@
     </rPh>
     <rPh sb="6" eb="8">
       <t>シッパイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TaskDAO.java</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TaskBean.java</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>t_taskテーブルにアクセスするDAOクラス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク情報を保持するentityクラス</t>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ホジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -577,10 +599,10 @@
   </cellStyles>
   <dxfs count="4">
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -616,8 +638,8 @@
     </tableColumn>
     <tableColumn id="3" xr3:uid="{10D378EB-2420-4F6D-94EB-578C28C48887}" name="ファイル名"/>
     <tableColumn id="4" xr3:uid="{BD40918F-95FC-4779-9466-EEC593EC9C60}" name="内容"/>
-    <tableColumn id="8" xr3:uid="{17803444-57CA-4498-913B-24461371C283}" name="対応ユースケース" dataDxfId="0"/>
-    <tableColumn id="5" xr3:uid="{61E9B625-6B0A-43DC-B4E2-261AFA95DB79}" name="ファイル種類" dataDxfId="1">
+    <tableColumn id="8" xr3:uid="{17803444-57CA-4498-913B-24461371C283}" name="対応ユースケース" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{61E9B625-6B0A-43DC-B4E2-261AFA95DB79}" name="ファイル種類" dataDxfId="0">
       <calculatedColumnFormula>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{339BCFBD-8ACC-4A6E-AE26-4A3C9DF9F927}" name="ファイル種類番号"/>
@@ -1573,35 +1595,55 @@
       </c>
     </row>
     <row r="27" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C27" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>#N/A</v>
+      <c r="B27" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
+        <v>Model</v>
+      </c>
+      <c r="C27" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
+        <v>model.daoパッケージ</v>
+      </c>
+      <c r="D27" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G27" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>DAO</v>
+      </c>
+      <c r="H27">
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C28" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>#N/A</v>
+      <c r="B28" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
+        <v>Model</v>
+      </c>
+      <c r="C28" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
+        <v>model.entityパッケージ</v>
+      </c>
+      <c r="D28" t="s">
+        <v>75</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G28" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>Bean</v>
+      </c>
+      <c r="H28">
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">

--- a/document/TaskMan_ファイル一覧表.xlsx
+++ b/document/TaskMan_ファイル一覧表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user113\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E207C061-67E4-433F-9804-E77AFFF98CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{331F8EB3-8F45-43C0-96CA-84103D30B984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4A369B84-176A-4D0D-BFB9-664BDE7AD73A}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="83">
   <si>
     <t>配置場所</t>
     <rPh sb="0" eb="4">
@@ -540,6 +540,26 @@
     <rPh sb="6" eb="8">
       <t>ホジ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CategoryDAO.java</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>StatusDAO.java</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク登録/タスク編集</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>m_categoryテーブルにアクセスするDAOクラス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>m_statusテーブルにアクセスするDAOクラス</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -624,10 +644,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{35429287-11A2-4B0B-829A-C13AF3056B74}" name="テーブル2" displayName="テーブル2" ref="B3:H36" totalsRowShown="0">
-  <autoFilter ref="B3:H36" xr:uid="{35429287-11A2-4B0B-829A-C13AF3056B74}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:H36">
-    <sortCondition ref="B3:B36"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{35429287-11A2-4B0B-829A-C13AF3056B74}" name="テーブル2" displayName="テーブル2" ref="B3:H34" totalsRowShown="0">
+  <autoFilter ref="B3:H34" xr:uid="{35429287-11A2-4B0B-829A-C13AF3056B74}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:H34">
+    <sortCondition ref="B3:B34"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{69642642-975E-4315-A040-B5AFDBF52485}" name="レイヤ" dataDxfId="3">
@@ -965,7 +985,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1C5B600-9E48-4077-B262-F985B8C16AE8}">
-  <dimension ref="B3:H36"/>
+  <dimension ref="B3:H34"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="6" width="25.625" customWidth="1"/>
@@ -1647,35 +1667,55 @@
       </c>
     </row>
     <row r="29" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C29" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>#N/A</v>
+      <c r="B29" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
+        <v>Model</v>
+      </c>
+      <c r="C29" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
+        <v>model.daoパッケージ</v>
+      </c>
+      <c r="D29" t="s">
+        <v>78</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G29" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>DAO</v>
+      </c>
+      <c r="H29">
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C30" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>#N/A</v>
+      <c r="B30" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
+        <v>Model</v>
+      </c>
+      <c r="C30" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
+        <v>model.daoパッケージ</v>
+      </c>
+      <c r="D30" t="s">
+        <v>79</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G30" t="str">
+        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
+        <v>DAO</v>
+      </c>
+      <c r="H30">
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
@@ -1738,38 +1778,6 @@
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C35" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C36" t="e">
-        <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" t="e">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
         <v>#N/A</v>
       </c>

--- a/document/TaskMan_ファイル一覧表.xlsx
+++ b/document/TaskMan_ファイル一覧表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user113\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{331F8EB3-8F45-43C0-96CA-84103D30B984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A144ED4D-5AEB-430B-AECD-C82FD2229A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4A369B84-176A-4D0D-BFB9-664BDE7AD73A}"/>
   </bookViews>
@@ -105,10 +105,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>TaskListSeavlet.java</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>LoginServlet.java</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -125,18 +121,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>TaskEditSeavlet.java</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>TaskDelete-Seavlet.java</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>TaskAddSeavlet.java</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>CategoryBean.java</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -149,9 +133,6 @@
   </si>
   <si>
     <t>jspファイル</t>
-  </si>
-  <si>
-    <t>Seavlet</t>
   </si>
   <si>
     <t>DAO</t>
@@ -560,6 +541,26 @@
   </si>
   <si>
     <t>m_statusテーブルにアクセスするDAOクラス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Servlet</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TaskListServlet.java</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TaskDelete-Servlet.java</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TaskAddServlet.java</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TaskEditServlet.java</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -646,8 +647,8 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{35429287-11A2-4B0B-829A-C13AF3056B74}" name="テーブル2" displayName="テーブル2" ref="B3:H34" totalsRowShown="0">
   <autoFilter ref="B3:H34" xr:uid="{35429287-11A2-4B0B-829A-C13AF3056B74}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:H34">
-    <sortCondition ref="B3:B34"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B6:H30">
+    <sortCondition ref="H3:H34"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{69642642-975E-4315-A040-B5AFDBF52485}" name="レイヤ" dataDxfId="3">
@@ -1007,13 +1008,13 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
@@ -1026,17 +1027,17 @@
         <v>servletパッケージ</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G4" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>Seavlet</v>
+        <v>Servlet</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -1052,17 +1053,17 @@
         <v>servletパッケージ</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G5" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>Seavlet</v>
+        <v>Servlet</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -1071,27 +1072,27 @@
     <row r="6" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>Controller</v>
+        <v>View</v>
       </c>
       <c r="C6" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>servletパッケージ</v>
+        <v>webapp</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>66</v>
       </c>
       <c r="G6" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>Seavlet</v>
+        <v>jspファイル</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
@@ -1104,17 +1105,17 @@
         <v>servletパッケージ</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G7" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>Seavlet</v>
+        <v>Servlet</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -1130,17 +1131,17 @@
         <v>servletパッケージ</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G8" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>Seavlet</v>
+        <v>Servlet</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -1156,13 +1157,13 @@
         <v>model.daoパッケージ</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G9" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
@@ -1182,13 +1183,13 @@
         <v>model.entityパッケージ</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G10" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
@@ -1201,79 +1202,79 @@
     <row r="11" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>Model</v>
+        <v>View</v>
       </c>
       <c r="C11" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>model.entityパッケージ</v>
+        <v>webapp</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G11" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>Bean</v>
+        <v>jspファイル</v>
       </c>
       <c r="H11">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>Model</v>
+        <v>View</v>
       </c>
       <c r="C12" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>model.entityパッケージ</v>
+        <v>webapp</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G12" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>Bean</v>
+        <v>jspファイル</v>
       </c>
       <c r="H12">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>Model</v>
+        <v>View</v>
       </c>
       <c r="C13" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>model.daoパッケージ</v>
+        <v>webapp</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="G13" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>ConnectionManager</v>
+        <v>jspファイル</v>
       </c>
       <c r="H13">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
@@ -1289,10 +1290,10 @@
         <v>5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G14" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
@@ -1315,10 +1316,10 @@
         <v>6</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G15" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
@@ -1331,53 +1332,53 @@
     <row r="16" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>View</v>
+        <v>Controller</v>
       </c>
       <c r="C16" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>webapp</v>
+        <v>servletパッケージ</v>
       </c>
       <c r="D16" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="G16" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>jspファイル</v>
+        <v>Servlet</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>View</v>
+        <v>Model</v>
       </c>
       <c r="C17" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>webapp</v>
+        <v>model.daoパッケージ</v>
       </c>
       <c r="D17" t="s">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G17" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>jspファイル</v>
+        <v>DAO</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
@@ -1393,10 +1394,10 @@
         <v>9</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G18" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
@@ -1419,10 +1420,10 @@
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G19" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
@@ -1445,10 +1446,10 @@
         <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G20" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
@@ -1471,10 +1472,10 @@
         <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G21" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
@@ -1487,27 +1488,27 @@
     <row r="22" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>View</v>
+        <v>Model</v>
       </c>
       <c r="C22" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>webapp</v>
+        <v>model.daoパッケージ</v>
       </c>
       <c r="D22" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G22" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>jspファイル</v>
+        <v>DAO</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
@@ -1523,10 +1524,10 @@
         <v>14</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G23" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
@@ -1546,13 +1547,13 @@
         <v>webapp</v>
       </c>
       <c r="D24" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G24" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
@@ -1565,27 +1566,27 @@
     <row r="25" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$C$5,2,FALSE)</f>
-        <v>View</v>
+        <v>Model</v>
       </c>
       <c r="C25" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>webapp</v>
+        <v>model.entityパッケージ</v>
       </c>
       <c r="D25" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G25" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>jspファイル</v>
+        <v>Bean</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
@@ -1598,13 +1599,13 @@
         <v>webapp</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G26" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
@@ -1624,13 +1625,13 @@
         <v>model.daoパッケージ</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G27" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
@@ -1650,13 +1651,13 @@
         <v>model.entityパッケージ</v>
       </c>
       <c r="D28" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G28" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
@@ -1673,23 +1674,23 @@
       </c>
       <c r="C29" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類]],Sheet2!$B$1:$D$5,3,FALSE)</f>
-        <v>model.daoパッケージ</v>
+        <v>model.entityパッケージ</v>
       </c>
       <c r="D29" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G29" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>DAO</v>
+        <v>Bean</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
@@ -1702,20 +1703,20 @@
         <v>model.daoパッケージ</v>
       </c>
       <c r="D30" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="G30" t="str">
         <f>VLOOKUP(テーブル2[[#This Row],[ファイル種類番号]],Sheet2!$A$1:$B$5,2,FALSE)</f>
-        <v>DAO</v>
+        <v>ConnectionManager</v>
       </c>
       <c r="H30">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="2:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.4">
@@ -1785,8 +1786,9 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1805,13 +1807,13 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
@@ -1819,13 +1821,13 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
         <v>35</v>
-      </c>
-      <c r="D2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -1833,13 +1835,13 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -1847,13 +1849,13 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -1864,10 +1866,10 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
